--- a/output/통합_AI보안위협_매트릭스_v3.1_LITE.xlsx
+++ b/output/통합_AI보안위협_매트릭스_v3.1_LITE.xlsx
@@ -12004,12 +12004,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:Q131"/>
-  <mergeCells count="5">
-    <mergeCell ref="P3"/>
-    <mergeCell ref="Q3"/>
+  <mergeCells count="3">
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="G3:L3"/>
     <mergeCell ref="M3:O3"/>
-    <mergeCell ref="G3:L3"/>
-    <mergeCell ref="A3:F3"/>
   </mergeCells>
   <conditionalFormatting sqref="G5:G131">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
